--- a/Жим_программа_ПМ110.xlsx
+++ b/Жим_программа_ПМ110.xlsx
@@ -176,7 +176,7 @@
     <t xml:space="preserve">• Колонка «КПШ» — количество подъёмов штанги, перенесено с фотографии как есть. Колонка «Расчёт КПШ» пересчитывает эту же сумму формулой по ячейкам строки: 21 строка из 22 совпадает.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Единственное расхождение — неделя 1, тренировка II (Пт): на фото КПШ = 48, а сумма подъёмов по ячейкам = 45. Строка перепроверена многократно при сильном увеличении: пустые ячейки действительно пусты, цифры читаются однозначно. Похоже, расхождение в 3 подъёма есть в самом исходном файле.</t>
+    <t xml:space="preserve">• Единственное расхождение — неделя 1, тренировка II (Пт): на фото КПШ = 48, а сумма подъёмов по ячейкам = 45. Строка разобрана попиксельно: пустые ячейки действительно пусты, начертание цифр сверено с эталонами из той же таблицы (в частности, последняя «5» — именно 5, а не 8). Похоже, расхождение в 3 подъёма есть в самом исходном файле. Вероятная причина: убывающая лесенка здесь идёт 2*3 - 4 - 6 - 5, тогда как в такой же по построению тренировке недели 4 она идёт 2*3 - 4 - 6 - 8. Если в последней ячейке (50%) должно стоять 8, сумма даёт ровно 48. В таблице оставлено то, что напечатано на фото — 5.</t>
   </si>
   <si>
     <t xml:space="preserve">• Неделя 4, тренировка III (Пт): значение КПШ на фото частично перекрыто курсором мыши; восстановлено по контрольной сумме ячеек — 53.</t>
